--- a/feedback_forms/042_mobile_arcade_gaming_feedback--feedback_forms.xlsx
+++ b/feedback_forms/042_mobile_arcade_gaming_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>how_often_do_you_play</t>
+          <t>how_much_time_do_you_play</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often do you play?</t>
+          <t>How much time do you play?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_much_time_do_you_play</t>
+          <t>favorite_genre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How much time do you play?</t>
+          <t>Favorite Genre</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,35 +635,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>favorite_genre</t>
+          <t>favorite_platform</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Favorite Genre</t>
+          <t>Favorite Platform</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>favorite_platform</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Favorite Platform</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,58 +681,58 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>how_often_do_you_play</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you play?</t>
+          <t>How would you rate your experience with mobile arcade games?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>favorite_title</t>
+          <t>play_time_next_month</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Favorite Title</t>
+          <t>How often do you think you will play next month?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_often_do_you_play</t>
+          <t>favorite_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you play?</t>
+          <t>Favorite type of game?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,113 +745,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>how_much_time_do_you_play</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How much time do you play?</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>favorite_genre</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Favorite Genre</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>favorite_platform</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Favorite Platform</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1093,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_often_do_you_play_choices</t>
+          <t>play_time_next_month_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1202,7 +1110,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>how_often_do_you_play_choices</t>
+          <t>play_time_next_month_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1219,7 +1127,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>how_often_do_you_play_choices</t>
+          <t>play_time_next_month_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1236,7 +1144,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>how_often_do_you_play_choices</t>
+          <t>play_time_next_month_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1247,227 +1155,6 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_play_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1-2_hours</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1-2 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_play_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2-4_hours</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2-4 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_play_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>4-6_hours</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>4-6 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_play_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>more_than_6_hours</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>More than 6 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>favorite_genre_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>favorite_genre_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>role_playing</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Role Playing</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>favorite_genre_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>favorite_genre_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>favorite_genre_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>simulation</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Simulation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>favorite_platform_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>console</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>favorite_platform_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>favorite_platform_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>favorite_platform_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>handheld</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Handheld</t>
         </is>
       </c>
     </row>
